--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/5.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/5.xlsx
@@ -426,13 +426,13 @@
         <v>-20.86233718706389</v>
       </c>
       <c r="E2">
-        <v>-7.736256875503319</v>
+        <v>-7.072649765945297</v>
       </c>
       <c r="F2">
-        <v>-0.6024692982630576</v>
+        <v>-1.137038144078235</v>
       </c>
       <c r="G2">
-        <v>-12.42920270803764</v>
+        <v>-12.98751297105357</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.34439274423509</v>
       </c>
       <c r="E3">
-        <v>-8.185196203201734</v>
+        <v>-8.821392459591328</v>
       </c>
       <c r="F3">
-        <v>-0.2377220296134099</v>
+        <v>-1.32323840782124</v>
       </c>
       <c r="G3">
-        <v>-12.39750092395358</v>
+        <v>-13.39853706302732</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.70224819042828</v>
       </c>
       <c r="E4">
-        <v>-8.776587737759437</v>
+        <v>-10.50128876289875</v>
       </c>
       <c r="F4">
-        <v>-0.3487350631679689</v>
+        <v>-1.028014245153468</v>
       </c>
       <c r="G4">
-        <v>-12.82201217845432</v>
+        <v>-12.38964499938889</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.04009631355728</v>
       </c>
       <c r="E5">
-        <v>-9.210904622887085</v>
+        <v>-9.027034992753647</v>
       </c>
       <c r="F5">
-        <v>-0.403753798523293</v>
+        <v>-0.7934951139304061</v>
       </c>
       <c r="G5">
-        <v>-11.64747034766738</v>
+        <v>-12.49087817143426</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.40024748723001</v>
       </c>
       <c r="E6">
-        <v>-10.06607071144357</v>
+        <v>-9.827429188187359</v>
       </c>
       <c r="F6">
-        <v>0.09614218183221088</v>
+        <v>-0.8076661144617583</v>
       </c>
       <c r="G6">
-        <v>-11.20277138646816</v>
+        <v>-11.824889104208</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.83907631001491</v>
       </c>
       <c r="E7">
-        <v>-10.42896903299625</v>
+        <v>-9.849288132222384</v>
       </c>
       <c r="F7">
-        <v>-0.1560772385547601</v>
+        <v>-0.5583219121642676</v>
       </c>
       <c r="G7">
-        <v>-11.5584266042976</v>
+        <v>-12.74637283397306</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.38372807256722</v>
       </c>
       <c r="E8">
-        <v>-11.2988753044477</v>
+        <v>-10.99510073953917</v>
       </c>
       <c r="F8">
-        <v>0.1755784949917804</v>
+        <v>-1.040268169674181</v>
       </c>
       <c r="G8">
-        <v>-11.69721129439493</v>
+        <v>-12.27408047570401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.05282008766602</v>
       </c>
       <c r="E9">
-        <v>-12.09185638793086</v>
+        <v>-11.71895919576924</v>
       </c>
       <c r="F9">
-        <v>0.3209500283817981</v>
+        <v>-0.6165231045566673</v>
       </c>
       <c r="G9">
-        <v>-11.46584719829188</v>
+        <v>-11.16259460580356</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.84363476654765</v>
       </c>
       <c r="E10">
-        <v>-12.28022732122792</v>
+        <v>-12.12446140078609</v>
       </c>
       <c r="F10">
-        <v>0.384778919744712</v>
+        <v>-0.1902567796217742</v>
       </c>
       <c r="G10">
-        <v>-11.07744737453351</v>
+        <v>-10.93444504941915</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.7368059871092</v>
       </c>
       <c r="E11">
-        <v>-13.42979856197107</v>
+        <v>-12.28065299778464</v>
       </c>
       <c r="F11">
-        <v>0.5954529828519599</v>
+        <v>-0.3624246171010274</v>
       </c>
       <c r="G11">
-        <v>-11.1045739846823</v>
+        <v>-12.14353904399947</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.69793691702907</v>
       </c>
       <c r="E12">
-        <v>-12.81332833835889</v>
+        <v>-12.55785900569018</v>
       </c>
       <c r="F12">
-        <v>0.6567471528972127</v>
+        <v>0.07419360155013559</v>
       </c>
       <c r="G12">
-        <v>-10.90688475780471</v>
+        <v>-11.2390152390321</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.68058432915624</v>
       </c>
       <c r="E13">
-        <v>-14.02369887112903</v>
+        <v>-13.48821587667002</v>
       </c>
       <c r="F13">
-        <v>1.157624239067331</v>
+        <v>0.2112728507669124</v>
       </c>
       <c r="G13">
-        <v>-10.38664907903594</v>
+        <v>-11.12046129272526</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.64191312835867</v>
       </c>
       <c r="E14">
-        <v>-14.55098985610816</v>
+        <v>-15.57806134646982</v>
       </c>
       <c r="F14">
-        <v>1.760971849084129</v>
+        <v>0.1658513732591513</v>
       </c>
       <c r="G14">
-        <v>-9.648596056510826</v>
+        <v>-10.82899755290228</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.5412981934817</v>
       </c>
       <c r="E15">
-        <v>-15.7043378441737</v>
+        <v>-14.53447451140218</v>
       </c>
       <c r="F15">
-        <v>1.587175961923804</v>
+        <v>0.5166066001458915</v>
       </c>
       <c r="G15">
-        <v>-10.25845151357321</v>
+        <v>-9.014543822101912</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.34703097637443</v>
       </c>
       <c r="E16">
-        <v>-15.3450849441972</v>
+        <v>-15.94708669335487</v>
       </c>
       <c r="F16">
-        <v>2.04187851842337</v>
+        <v>0.8898385732375061</v>
       </c>
       <c r="G16">
-        <v>-9.195637284191125</v>
+        <v>-8.983570358036491</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.04431770495039</v>
       </c>
       <c r="E17">
-        <v>-15.88732442187565</v>
+        <v>-16.27723961935809</v>
       </c>
       <c r="F17">
-        <v>2.247467301836142</v>
+        <v>1.208233145301114</v>
       </c>
       <c r="G17">
-        <v>-8.947909161487463</v>
+        <v>-9.256958519215045</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.63388208141423</v>
       </c>
       <c r="E18">
-        <v>-17.5737371992801</v>
+        <v>-18.43954520175462</v>
       </c>
       <c r="F18">
-        <v>2.250618876607866</v>
+        <v>1.060389446977096</v>
       </c>
       <c r="G18">
-        <v>-8.715839919184551</v>
+        <v>-8.929724334840245</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.13330536886183</v>
       </c>
       <c r="E19">
-        <v>-18.76453113891508</v>
+        <v>-18.8319646453633</v>
       </c>
       <c r="F19">
-        <v>2.717919813664753</v>
+        <v>2.167341284750398</v>
       </c>
       <c r="G19">
-        <v>-8.538778701562171</v>
+        <v>-8.300005604542237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.57084209113178</v>
       </c>
       <c r="E20">
-        <v>-18.42208793445505</v>
+        <v>-19.21303120463475</v>
       </c>
       <c r="F20">
-        <v>3.103525281073696</v>
+        <v>2.047088910885166</v>
       </c>
       <c r="G20">
-        <v>-8.245762315881279</v>
+        <v>-8.410044827722071</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.97829932708486</v>
       </c>
       <c r="E21">
-        <v>-19.34532604429483</v>
+        <v>-19.45184028142925</v>
       </c>
       <c r="F21">
-        <v>3.256968963514709</v>
+        <v>2.167355538103637</v>
       </c>
       <c r="G21">
-        <v>-7.821393414838723</v>
+        <v>-8.593886042608879</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.38494369787541</v>
       </c>
       <c r="E22">
-        <v>-20.20912793278395</v>
+        <v>-20.28068235057914</v>
       </c>
       <c r="F22">
-        <v>3.62878510351792</v>
+        <v>2.562003966289739</v>
       </c>
       <c r="G22">
-        <v>-7.872408921598892</v>
+        <v>-8.620711393113593</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.81526005065415</v>
       </c>
       <c r="E23">
-        <v>-20.37602484233664</v>
+        <v>-21.65872869043129</v>
       </c>
       <c r="F23">
-        <v>3.696307988928596</v>
+        <v>2.541016695498336</v>
       </c>
       <c r="G23">
-        <v>-7.757029788464212</v>
+        <v>-7.910314668023547</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.28733849822976</v>
       </c>
       <c r="E24">
-        <v>-20.20900113551173</v>
+        <v>-20.63993977902966</v>
       </c>
       <c r="F24">
-        <v>3.623539869525985</v>
+        <v>2.135447031319363</v>
       </c>
       <c r="G24">
-        <v>-7.846745572578461</v>
+        <v>-7.373420324101164</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.81391080197308</v>
       </c>
       <c r="E25">
-        <v>-22.01831216901035</v>
+        <v>-21.95176624346764</v>
       </c>
       <c r="F25">
-        <v>3.729350429148325</v>
+        <v>2.61523548951949</v>
       </c>
       <c r="G25">
-        <v>-8.08118516548749</v>
+        <v>-7.642739824811954</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.40008645438331</v>
       </c>
       <c r="E26">
-        <v>-20.96567291440138</v>
+        <v>-21.44445941428436</v>
       </c>
       <c r="F26">
-        <v>3.580235014974209</v>
+        <v>2.572860270340077</v>
       </c>
       <c r="G26">
-        <v>-8.187274907838974</v>
+        <v>-7.657097660815772</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.04238357754726</v>
       </c>
       <c r="E27">
-        <v>-20.51626262540617</v>
+        <v>-21.8696242534425</v>
       </c>
       <c r="F27">
-        <v>3.305414527468001</v>
+        <v>2.482783828987627</v>
       </c>
       <c r="G27">
-        <v>-7.612027893844135</v>
+        <v>-7.130634845887633</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.73396346274129</v>
       </c>
       <c r="E28">
-        <v>-20.83023531377998</v>
+        <v>-21.02594690344348</v>
       </c>
       <c r="F28">
-        <v>3.465539865166253</v>
+        <v>2.412204391160153</v>
       </c>
       <c r="G28">
-        <v>-8.00106003180051</v>
+        <v>-7.478672498431212</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.46379872123126</v>
       </c>
       <c r="E29">
-        <v>-21.50093854210802</v>
+        <v>-21.68750261427602</v>
       </c>
       <c r="F29">
-        <v>3.346662148035622</v>
+        <v>2.047003390765732</v>
       </c>
       <c r="G29">
-        <v>-7.873084272888903</v>
+        <v>-7.891656433364215</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.22712243922646</v>
       </c>
       <c r="E30">
-        <v>-21.21356158158126</v>
+        <v>-22.54676244333545</v>
       </c>
       <c r="F30">
-        <v>3.533865689476057</v>
+        <v>2.469974815543553</v>
       </c>
       <c r="G30">
-        <v>-7.590870197302652</v>
+        <v>-7.563164241684492</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.02250045218048</v>
       </c>
       <c r="E31">
-        <v>-21.46625043120927</v>
+        <v>-21.93799515401031</v>
       </c>
       <c r="F31">
-        <v>3.324890942816075</v>
+        <v>2.286402711767221</v>
       </c>
       <c r="G31">
-        <v>-7.013620303256554</v>
+        <v>-8.015642984901</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.849867172105144</v>
       </c>
       <c r="E32">
-        <v>-21.25575337391072</v>
+        <v>-19.65020555686124</v>
       </c>
       <c r="F32">
-        <v>3.042373644560833</v>
+        <v>1.839784973965973</v>
       </c>
       <c r="G32">
-        <v>-7.354901132354481</v>
+        <v>-7.408849782462444</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.708889577879319</v>
       </c>
       <c r="E33">
-        <v>-20.42076163705841</v>
+        <v>-20.98700655545152</v>
       </c>
       <c r="F33">
-        <v>3.043977938653172</v>
+        <v>1.940507086482006</v>
       </c>
       <c r="G33">
-        <v>-7.054402913754835</v>
+        <v>-6.330346877769755</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.595541775155546</v>
       </c>
       <c r="E34">
-        <v>-21.15532540584262</v>
+        <v>-19.04772378945875</v>
       </c>
       <c r="F34">
-        <v>2.869171647118797</v>
+        <v>2.116488487805638</v>
       </c>
       <c r="G34">
-        <v>-6.621658332497923</v>
+        <v>-7.591618380594528</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.506209358172171</v>
       </c>
       <c r="E35">
-        <v>-19.52388830289128</v>
+        <v>-20.05446695999998</v>
       </c>
       <c r="F35">
-        <v>3.184089984698016</v>
+        <v>1.721664268262922</v>
       </c>
       <c r="G35">
-        <v>-6.929201392005139</v>
+        <v>-7.510877485437243</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.436734064659914</v>
       </c>
       <c r="E36">
-        <v>-20.34514517807833</v>
+        <v>-19.78781682500632</v>
       </c>
       <c r="F36">
-        <v>2.99198328974338</v>
+        <v>2.080958045592753</v>
       </c>
       <c r="G36">
-        <v>-6.532329882211769</v>
+        <v>-6.39064846476758</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.381465909270185</v>
       </c>
       <c r="E37">
-        <v>-19.45681254588967</v>
+        <v>-19.12341270402295</v>
       </c>
       <c r="F37">
-        <v>3.093996122580497</v>
+        <v>1.798570611222577</v>
       </c>
       <c r="G37">
-        <v>-6.637906490004666</v>
+        <v>-5.568666491730858</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.33358663437059</v>
       </c>
       <c r="E38">
-        <v>-19.09275946346503</v>
+        <v>-19.0669381046733</v>
       </c>
       <c r="F38">
-        <v>2.85860357754507</v>
+        <v>2.08835236851194</v>
       </c>
       <c r="G38">
-        <v>-6.238747393243661</v>
+        <v>-6.846735702621893</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.286370537916246</v>
       </c>
       <c r="E39">
-        <v>-19.38129571333776</v>
+        <v>-19.44603477775141</v>
       </c>
       <c r="F39">
-        <v>3.202133146192617</v>
+        <v>1.748701295651304</v>
       </c>
       <c r="G39">
-        <v>-5.58701022456396</v>
+        <v>-5.74553569771196</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.234950645601588</v>
       </c>
       <c r="E40">
-        <v>-18.55060602679273</v>
+        <v>-18.23138030857002</v>
       </c>
       <c r="F40">
-        <v>2.690048173258934</v>
+        <v>2.107336251320313</v>
       </c>
       <c r="G40">
-        <v>-5.399825358682489</v>
+        <v>-5.619609166489163</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.17809584962075</v>
       </c>
       <c r="E41">
-        <v>-19.16402405892374</v>
+        <v>-18.37283625114762</v>
       </c>
       <c r="F41">
-        <v>3.301048250259135</v>
+        <v>2.264496891544862</v>
       </c>
       <c r="G41">
-        <v>-5.915724222794814</v>
+        <v>-5.833774978515695</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.117838304290187</v>
       </c>
       <c r="E42">
-        <v>-19.169489927051</v>
+        <v>-18.91162956010623</v>
       </c>
       <c r="F42">
-        <v>2.935104491790372</v>
+        <v>2.126239365126998</v>
       </c>
       <c r="G42">
-        <v>-6.117664190144817</v>
+        <v>-6.4462457665541</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.055672030496927</v>
       </c>
       <c r="E43">
-        <v>-18.91318735516487</v>
+        <v>-17.84445390393265</v>
       </c>
       <c r="F43">
-        <v>2.971759365203218</v>
+        <v>2.202140054830349</v>
       </c>
       <c r="G43">
-        <v>-5.412951671745699</v>
+        <v>-6.315873172672061</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.992956158040606</v>
       </c>
       <c r="E44">
-        <v>-18.8669154077545</v>
+        <v>-17.75582713912853</v>
       </c>
       <c r="F44">
-        <v>3.305739187180667</v>
+        <v>1.659480055493192</v>
       </c>
       <c r="G44">
-        <v>-5.773685266432384</v>
+        <v>-6.153093648506097</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.929093196488035</v>
       </c>
       <c r="E45">
-        <v>-17.98483206969642</v>
+        <v>-17.45225635555034</v>
       </c>
       <c r="F45">
-        <v>2.904865211040971</v>
+        <v>1.931882224066523</v>
       </c>
       <c r="G45">
-        <v>-6.069601690005678</v>
+        <v>-6.144469677376296</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.865840843773093</v>
       </c>
       <c r="E46">
-        <v>-18.10019494504182</v>
+        <v>-17.75915556752417</v>
       </c>
       <c r="F46">
-        <v>2.613176671829419</v>
+        <v>2.096795104747148</v>
       </c>
       <c r="G46">
-        <v>-6.143413613349268</v>
+        <v>-6.094013652812264</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.806592370399958</v>
       </c>
       <c r="E47">
-        <v>-17.91573661328739</v>
+        <v>-17.9383563409557</v>
       </c>
       <c r="F47">
-        <v>2.848173290385986</v>
+        <v>1.660194306861055</v>
       </c>
       <c r="G47">
-        <v>-5.857981687498846</v>
+        <v>-6.162290344014193</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.753413932738798</v>
       </c>
       <c r="E48">
-        <v>-16.94488612773095</v>
+        <v>-16.86082859320058</v>
       </c>
       <c r="F48">
-        <v>2.862768724102676</v>
+        <v>1.948370186352163</v>
       </c>
       <c r="G48">
-        <v>-6.321861949552603</v>
+        <v>-6.68944506296004</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.708037971497731</v>
       </c>
       <c r="E49">
-        <v>-16.39392028063972</v>
+        <v>-16.56989678057779</v>
       </c>
       <c r="F49">
-        <v>2.771700882847161</v>
+        <v>1.512398119714499</v>
       </c>
       <c r="G49">
-        <v>-6.480864141258259</v>
+        <v>-7.190357087416085</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.668384381373139</v>
       </c>
       <c r="E50">
-        <v>-16.66163007855117</v>
+        <v>-16.6748713365496</v>
       </c>
       <c r="F50">
-        <v>2.913990524525734</v>
+        <v>1.942290339342791</v>
       </c>
       <c r="G50">
-        <v>-6.412653660967115</v>
+        <v>-7.255829746546251</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.631008882647041</v>
       </c>
       <c r="E51">
-        <v>-16.07918680863262</v>
+        <v>-15.48219808020144</v>
       </c>
       <c r="F51">
-        <v>3.003978278346918</v>
+        <v>1.659271006312353</v>
       </c>
       <c r="G51">
-        <v>-6.055482213280686</v>
+        <v>-6.366805915793749</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.593248041835944</v>
       </c>
       <c r="E52">
-        <v>-16.74651179535094</v>
+        <v>-15.49862738390127</v>
       </c>
       <c r="F52">
-        <v>2.36847827083487</v>
+        <v>1.540999848547336</v>
       </c>
       <c r="G52">
-        <v>-6.632950603332377</v>
+        <v>-7.467204768683177</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.554128353176338</v>
       </c>
       <c r="E53">
-        <v>-16.74213728945954</v>
+        <v>-16.55282896204288</v>
       </c>
       <c r="F53">
-        <v>2.274650030168744</v>
+        <v>1.726439141597971</v>
       </c>
       <c r="G53">
-        <v>-6.436741190310853</v>
+        <v>-6.518111089120599</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.513342965507768</v>
       </c>
       <c r="E54">
-        <v>-15.88446695477681</v>
+        <v>-15.11515167645774</v>
       </c>
       <c r="F54">
-        <v>2.485026356563889</v>
+        <v>1.568002034405578</v>
       </c>
       <c r="G54">
-        <v>-7.086528447667923</v>
+        <v>-7.338517242480628</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.471553500086063</v>
       </c>
       <c r="E55">
-        <v>-15.68415896399553</v>
+        <v>-15.23656459307739</v>
       </c>
       <c r="F55">
-        <v>2.608260848667895</v>
+        <v>1.07683781661485</v>
       </c>
       <c r="G55">
-        <v>-6.368202966011322</v>
+        <v>-6.212090880561449</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.432108039724495</v>
       </c>
       <c r="E56">
-        <v>-17.10855423531617</v>
+        <v>-14.48267782570245</v>
       </c>
       <c r="F56">
-        <v>2.261300973007505</v>
+        <v>1.297969089881744</v>
       </c>
       <c r="G56">
-        <v>-6.572139192321505</v>
+        <v>-6.968487635919669</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.400537652004671</v>
       </c>
       <c r="E57">
-        <v>-14.74715882164643</v>
+        <v>-13.71350293007762</v>
       </c>
       <c r="F57">
-        <v>2.556104661754727</v>
+        <v>1.555205690608827</v>
       </c>
       <c r="G57">
-        <v>-7.497718066918639</v>
+        <v>-7.710321301450636</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.383739992289865</v>
       </c>
       <c r="E58">
-        <v>-15.98310617561188</v>
+        <v>-15.15876993809962</v>
       </c>
       <c r="F58">
-        <v>2.130938220578107</v>
+        <v>1.602857817898485</v>
       </c>
       <c r="G58">
-        <v>-7.580547916311205</v>
+        <v>-7.506530739144179</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.386442919525699</v>
       </c>
       <c r="E59">
-        <v>-15.41524459199804</v>
+        <v>-13.10423298013763</v>
       </c>
       <c r="F59">
-        <v>2.611618305208626</v>
+        <v>1.083850466408416</v>
       </c>
       <c r="G59">
-        <v>-6.46887003476948</v>
+        <v>-7.873842387817397</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.411828818448829</v>
       </c>
       <c r="E60">
-        <v>-15.64076259758002</v>
+        <v>-14.26390271791788</v>
       </c>
       <c r="F60">
-        <v>2.046830766820949</v>
+        <v>1.345779587762946</v>
       </c>
       <c r="G60">
-        <v>-7.21399769311202</v>
+        <v>-7.526268211649315</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.460259918119833</v>
       </c>
       <c r="E61">
-        <v>-15.65517673034643</v>
+        <v>-13.40858718971915</v>
       </c>
       <c r="F61">
-        <v>2.225624829850401</v>
+        <v>1.088166065027988</v>
       </c>
       <c r="G61">
-        <v>-7.512453305113936</v>
+        <v>-7.222641527515058</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.532105266292465</v>
       </c>
       <c r="E62">
-        <v>-15.66480879456075</v>
+        <v>-13.62815478045505</v>
       </c>
       <c r="F62">
-        <v>2.754148670186346</v>
+        <v>1.796174464172517</v>
       </c>
       <c r="G62">
-        <v>-7.711052932014814</v>
+        <v>-7.839737147671825</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.627985820927444</v>
       </c>
       <c r="E63">
-        <v>-15.00156849139735</v>
+        <v>-14.54284765984236</v>
       </c>
       <c r="F63">
-        <v>2.08487296661572</v>
+        <v>1.235002526389787</v>
       </c>
       <c r="G63">
-        <v>-7.158347422596872</v>
+        <v>-8.243269475090207</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.743122234604268</v>
       </c>
       <c r="E64">
-        <v>-14.97840534684812</v>
+        <v>-13.01512166861469</v>
       </c>
       <c r="F64">
-        <v>2.054971015226307</v>
+        <v>1.25041990347659</v>
       </c>
       <c r="G64">
-        <v>-7.370672571303569</v>
+        <v>-7.843852155777139</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.869906692322486</v>
       </c>
       <c r="E65">
-        <v>-14.13821039336099</v>
+        <v>-13.44265489967885</v>
       </c>
       <c r="F65">
-        <v>2.485892643699635</v>
+        <v>1.623788075276933</v>
       </c>
       <c r="G65">
-        <v>-7.246682709221245</v>
+        <v>-7.201265334967983</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.999895455824349</v>
       </c>
       <c r="E66">
-        <v>-15.07914125114874</v>
+        <v>-13.62781967337848</v>
       </c>
       <c r="F66">
-        <v>1.971446365246031</v>
+        <v>1.091035740146764</v>
       </c>
       <c r="G66">
-        <v>-7.134074502702935</v>
+        <v>-8.144810540206743</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.128637230454755</v>
       </c>
       <c r="E67">
-        <v>-15.63389743098439</v>
+        <v>-13.80989149933088</v>
       </c>
       <c r="F67">
-        <v>2.538137518144067</v>
+        <v>1.231494617787089</v>
       </c>
       <c r="G67">
-        <v>-7.65987851906876</v>
+        <v>-7.617099649610299</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.25400404406659</v>
       </c>
       <c r="E68">
-        <v>-15.2042765734027</v>
+        <v>-14.22149808731006</v>
       </c>
       <c r="F68">
-        <v>1.864345085302608</v>
+        <v>1.067351418181367</v>
       </c>
       <c r="G68">
-        <v>-7.641445401506099</v>
+        <v>-8.101611231464794</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.373117300162528</v>
       </c>
       <c r="E69">
-        <v>-15.22862164966793</v>
+        <v>-13.64679397947062</v>
       </c>
       <c r="F69">
-        <v>1.965288916646803</v>
+        <v>0.9700089340888818</v>
       </c>
       <c r="G69">
-        <v>-8.099161427765733</v>
+        <v>-8.28768044349953</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.480887461490749</v>
       </c>
       <c r="E70">
-        <v>-15.60377402188537</v>
+        <v>-12.74690468161439</v>
       </c>
       <c r="F70">
-        <v>2.141218055675224</v>
+        <v>0.788519403591352</v>
       </c>
       <c r="G70">
-        <v>-7.874421733286769</v>
+        <v>-7.964303044677981</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.571442003502193</v>
       </c>
       <c r="E71">
-        <v>-14.46975808935857</v>
+        <v>-13.13327408394882</v>
       </c>
       <c r="F71">
-        <v>2.157496968780027</v>
+        <v>1.007773985348451</v>
       </c>
       <c r="G71">
-        <v>-7.59846458876974</v>
+        <v>-8.394809697150347</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.641353772434499</v>
       </c>
       <c r="E72">
-        <v>-16.13943362683067</v>
+        <v>-13.81504943122562</v>
       </c>
       <c r="F72">
-        <v>1.982505383653545</v>
+        <v>1.238713149349662</v>
       </c>
       <c r="G72">
-        <v>-8.206631667607093</v>
+        <v>-8.286647553291278</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.690794099704471</v>
       </c>
       <c r="E73">
-        <v>-16.08773656755911</v>
+        <v>-14.29852743018053</v>
       </c>
       <c r="F73">
-        <v>1.951109997585873</v>
+        <v>0.7480145410980727</v>
       </c>
       <c r="G73">
-        <v>-8.046000687496116</v>
+        <v>-8.633188839251106</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.722737086440835</v>
       </c>
       <c r="E74">
-        <v>-15.8437288026038</v>
+        <v>-14.73937890330125</v>
       </c>
       <c r="F74">
-        <v>1.956747990644838</v>
+        <v>0.4965790551392443</v>
       </c>
       <c r="G74">
-        <v>-8.513512618006454</v>
+        <v>-7.924225580379565</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.738815762871784</v>
       </c>
       <c r="E75">
-        <v>-16.36340289430203</v>
+        <v>-14.64929849834067</v>
       </c>
       <c r="F75">
-        <v>1.888952707816706</v>
+        <v>0.7187951669582149</v>
       </c>
       <c r="G75">
-        <v>-8.412719748517803</v>
+        <v>-8.316674201332468</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.740789136399615</v>
       </c>
       <c r="E76">
-        <v>-16.37807967856089</v>
+        <v>-14.9014122317697</v>
       </c>
       <c r="F76">
-        <v>1.620250076261841</v>
+        <v>0.9652388118715782</v>
       </c>
       <c r="G76">
-        <v>-7.914959363415145</v>
+        <v>-8.341837657976468</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.72922235803245</v>
       </c>
       <c r="E77">
-        <v>-16.68129271269247</v>
+        <v>-15.24274596009786</v>
       </c>
       <c r="F77">
-        <v>1.626790781692606</v>
+        <v>1.035013727094009</v>
       </c>
       <c r="G77">
-        <v>-8.359952963167359</v>
+        <v>-8.436929768046493</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.70515859234628</v>
       </c>
       <c r="E78">
-        <v>-16.95492575460596</v>
+        <v>-16.44017411415407</v>
       </c>
       <c r="F78">
-        <v>1.525587222578279</v>
+        <v>0.4508154971537483</v>
       </c>
       <c r="G78">
-        <v>-7.999209436844057</v>
+        <v>-8.708709004092961</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.670780715484844</v>
       </c>
       <c r="E79">
-        <v>-17.70966387509434</v>
+        <v>-15.98222765165439</v>
       </c>
       <c r="F79">
-        <v>1.899299058562272</v>
+        <v>0.9007313025238987</v>
       </c>
       <c r="G79">
-        <v>-8.005919912652161</v>
+        <v>-8.029947852176189</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.62465424930336</v>
       </c>
       <c r="E80">
-        <v>-17.72356176182388</v>
+        <v>-16.2989717661209</v>
       </c>
       <c r="F80">
-        <v>1.561721056744945</v>
+        <v>0.3897066207006018</v>
       </c>
       <c r="G80">
-        <v>-9.087531419606224</v>
+        <v>-8.530002445337564</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.563418096146982</v>
       </c>
       <c r="E81">
-        <v>-19.07869855167122</v>
+        <v>-16.64921753129615</v>
       </c>
       <c r="F81">
-        <v>1.333699079039974</v>
+        <v>0.4106004528429944</v>
       </c>
       <c r="G81">
-        <v>-8.672554536258581</v>
+        <v>-8.036482869070712</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.480341521587102</v>
       </c>
       <c r="E82">
-        <v>-19.29479280284324</v>
+        <v>-16.98543861246964</v>
       </c>
       <c r="F82">
-        <v>1.578638203333669</v>
+        <v>0.5227703835687819</v>
       </c>
       <c r="G82">
-        <v>-8.213378559416128</v>
+        <v>-8.203764735170084</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.370753194484159</v>
       </c>
       <c r="E83">
-        <v>-19.84821761132063</v>
+        <v>-19.16728908868327</v>
       </c>
       <c r="F83">
-        <v>1.469644394821296</v>
+        <v>0.8039621199728021</v>
       </c>
       <c r="G83">
-        <v>-8.327450027062795</v>
+        <v>-7.624578171983512</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.231655683642892</v>
       </c>
       <c r="E84">
-        <v>-20.01386919052122</v>
+        <v>-19.71011726798272</v>
       </c>
       <c r="F84">
-        <v>1.357346975769316</v>
+        <v>0.556164406501738</v>
       </c>
       <c r="G84">
-        <v>-8.69840658637475</v>
+        <v>-8.78070674848103</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.06109240983324</v>
       </c>
       <c r="E85">
-        <v>-21.41837540400018</v>
+        <v>-20.718074069558</v>
       </c>
       <c r="F85">
-        <v>1.003087799544666</v>
+        <v>0.4435328255016</v>
       </c>
       <c r="G85">
-        <v>-8.389814083931586</v>
+        <v>-8.735617118236158</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.856980414544381</v>
       </c>
       <c r="E86">
-        <v>-22.24542419744304</v>
+        <v>-20.91123159988117</v>
       </c>
       <c r="F86">
-        <v>1.243294810563028</v>
+        <v>0.4763131623923234</v>
       </c>
       <c r="G86">
-        <v>-7.997732933533542</v>
+        <v>-8.133624206829547</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.617497514646905</v>
       </c>
       <c r="E87">
-        <v>-23.95106940395807</v>
+        <v>-22.42422646516189</v>
       </c>
       <c r="F87">
-        <v>1.152849365732281</v>
+        <v>0.2094500052582416</v>
       </c>
       <c r="G87">
-        <v>-8.22195949345392</v>
+        <v>-8.667264284486825</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.34495828904071</v>
       </c>
       <c r="E88">
-        <v>-25.90446742343275</v>
+        <v>-24.30707538807107</v>
       </c>
       <c r="F88">
-        <v>1.239595273544562</v>
+        <v>0.3999492387087064</v>
       </c>
       <c r="G88">
-        <v>-7.979015109054503</v>
+        <v>-7.967113697840823</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.046233275921709</v>
       </c>
       <c r="E89">
-        <v>-26.73556467263846</v>
+        <v>-26.01449575639711</v>
       </c>
       <c r="F89">
-        <v>1.161542327502129</v>
+        <v>0.07748533429537648</v>
       </c>
       <c r="G89">
-        <v>-7.553894714174533</v>
+        <v>-8.250969804014552</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.730179261094221</v>
       </c>
       <c r="E90">
-        <v>-27.42724832104404</v>
+        <v>-26.62309549218396</v>
       </c>
       <c r="F90">
-        <v>1.074685560275767</v>
+        <v>0.2063285208989104</v>
       </c>
       <c r="G90">
-        <v>-7.417073177581994</v>
+        <v>-7.967544068760928</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.4052525207933</v>
       </c>
       <c r="E91">
-        <v>-30.30509128868155</v>
+        <v>-28.11928971889623</v>
       </c>
       <c r="F91">
-        <v>1.089954069006519</v>
+        <v>0.2915057680019479</v>
       </c>
       <c r="G91">
-        <v>-7.855862814993615</v>
+        <v>-7.931720655480475</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.080302905803277</v>
       </c>
       <c r="E92">
-        <v>-31.91290787120888</v>
+        <v>-30.47329239874845</v>
       </c>
       <c r="F92">
-        <v>1.101545212601621</v>
+        <v>0.2029267205925465</v>
       </c>
       <c r="G92">
-        <v>-7.091726004164578</v>
+        <v>-7.862715644259906</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.763921569598035</v>
       </c>
       <c r="E93">
-        <v>-34.03582252244968</v>
+        <v>-32.49052378783525</v>
       </c>
       <c r="F93">
-        <v>1.057323392324805</v>
+        <v>0.2592646829754317</v>
       </c>
       <c r="G93">
-        <v>-7.821505973387058</v>
+        <v>-7.201245471694748</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.466062968643992</v>
       </c>
       <c r="E94">
-        <v>-36.78954681024796</v>
+        <v>-34.16258130263539</v>
       </c>
       <c r="F94">
-        <v>0.9133233482575577</v>
+        <v>0.1412999723050513</v>
       </c>
       <c r="G94">
-        <v>-6.942797802534925</v>
+        <v>-6.646623156409567</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.196423734174272</v>
       </c>
       <c r="E95">
-        <v>-38.38020953323424</v>
+        <v>-37.34917336387886</v>
       </c>
       <c r="F95">
-        <v>0.9297843875426353</v>
+        <v>0.07720660205425912</v>
       </c>
       <c r="G95">
-        <v>-7.123686010800703</v>
+        <v>-7.631546870343677</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.963952053754419</v>
       </c>
       <c r="E96">
-        <v>-39.85244813244592</v>
+        <v>-38.45410970056541</v>
       </c>
       <c r="F96">
-        <v>1.33527011530809</v>
+        <v>0.4777131584215719</v>
       </c>
       <c r="G96">
-        <v>-7.20337084193096</v>
+        <v>-7.277709142015294</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.771444733151919</v>
       </c>
       <c r="E97">
-        <v>-43.01543325868741</v>
+        <v>-41.27398140819373</v>
       </c>
       <c r="F97">
-        <v>1.0847310068974</v>
+        <v>0.9044245047187034</v>
       </c>
       <c r="G97">
-        <v>-7.308334998799093</v>
+        <v>-6.879430650367735</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.622425035636747</v>
       </c>
       <c r="E98">
-        <v>-44.81025317536148</v>
+        <v>-43.82154012408179</v>
       </c>
       <c r="F98">
-        <v>1.27121079473448</v>
+        <v>0.5536447303902738</v>
       </c>
       <c r="G98">
-        <v>-7.428504491329097</v>
+        <v>-7.367825502139795</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.512346989196921</v>
       </c>
       <c r="E99">
-        <v>-47.01206742923793</v>
+        <v>-47.9428545052485</v>
       </c>
       <c r="F99">
-        <v>1.049040610387057</v>
+        <v>0.50756443122169</v>
       </c>
       <c r="G99">
-        <v>-7.107408058384106</v>
+        <v>-7.396342541415078</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.447564416483212</v>
       </c>
       <c r="E100">
-        <v>-50.18542955366799</v>
+        <v>-47.77451301248737</v>
       </c>
       <c r="F100">
-        <v>1.444708945182702</v>
+        <v>0.2030542089187394</v>
       </c>
       <c r="G100">
-        <v>-7.590429894745929</v>
+        <v>-8.096479885878923</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.408278712175964</v>
       </c>
       <c r="E101">
-        <v>-51.63321099688275</v>
+        <v>-50.75937287787414</v>
       </c>
       <c r="F101">
-        <v>1.251856324741894</v>
+        <v>0.3564226653287687</v>
       </c>
       <c r="G101">
-        <v>-7.905974542821562</v>
+        <v>-7.269422846530499</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.405283587022451</v>
       </c>
       <c r="E102">
-        <v>-54.48997957860706</v>
+        <v>-53.45907699923492</v>
       </c>
       <c r="F102">
-        <v>1.310635569793429</v>
+        <v>0.7455344576344946</v>
       </c>
       <c r="G102">
-        <v>-7.806102004992829</v>
+        <v>-7.352888320666604</v>
       </c>
     </row>
   </sheetData>
